--- a/modules/refactoring/seasonality_example.xlsx
+++ b/modules/refactoring/seasonality_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ale_c\OneDrive\Documents\GitHub\personal_website\modules\refactoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488AFF13-1AF8-4A26-B1F4-6E3397584B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEDB23B-C95D-49AD-864C-9CBAB66DE8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27810" yWindow="2610" windowWidth="21645" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26655" yWindow="1230" windowWidth="17025" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/modules/refactoring/seasonality_example.xlsx
+++ b/modules/refactoring/seasonality_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ale_c\OneDrive\Documents\GitHub\personal_website\modules\refactoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEDB23B-C95D-49AD-864C-9CBAB66DE8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2897B37F-01D9-44A5-A63A-DD6571A6677C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26655" yWindow="1230" windowWidth="17025" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16965" yWindow="13830" windowWidth="8010" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -344,67 +340,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
-        <v>4</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>3</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>5</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>6</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>8</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
